--- a/STEPS_data_analysis/templates/data_fromR.xlsx
+++ b/STEPS_data_analysis/templates/data_fromR.xlsx
@@ -1,40 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\GitHub current\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\Latest from Lucas\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9BB32A-150B-489F-A9E4-533E70AF421B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3838ED49-21FF-4DB5-A83E-601E275F168B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="17955" windowHeight="15030" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="languages" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="417">
   <si>
     <t>ind_level</t>
   </si>
@@ -111,9 +98,6 @@
     <t>Multiple Risk Factors</t>
   </si>
   <si>
-    <t>of the population have 0 risk factors</t>
-  </si>
-  <si>
     <t>english</t>
   </si>
   <si>
@@ -471,12 +455,6 @@
     <t>were advised to maintain healthy weight/lose weight</t>
   </si>
   <si>
-    <t>of the population have 3 to 5 risk factors</t>
-  </si>
-  <si>
-    <t>of the population have 1to 2 risk factors</t>
-  </si>
-  <si>
     <t>of 18-44 year olds have 3 to 5 risk factors</t>
   </si>
   <si>
@@ -660,15 +638,6 @@
     <t>ont été conseillés de maintenir un poids santé/de perdre du poids</t>
   </si>
   <si>
-    <t>de la population présentent 3 à 5 facteurs de risque</t>
-  </si>
-  <si>
-    <t>de la population présentent 1 à 2 facteurs de risque</t>
-  </si>
-  <si>
-    <t>de la population ne présente aucun facteur de risque</t>
-  </si>
-  <si>
     <t>des personnes âgées de 18 à 44 ans présentent de 3 à 5 facteurs de risque</t>
   </si>
   <si>
@@ -684,6 +653,15 @@
     <t>bm1l1</t>
   </si>
   <si>
+    <t>of the population aged 18-69 have 3 to 5 risk factors</t>
+  </si>
+  <si>
+    <t>of the population aged 18-69 have 0 risk factors</t>
+  </si>
+  <si>
+    <t>of the population aged 18-69 have 1 to 2 risk factors</t>
+  </si>
+  <si>
     <t>spanish</t>
   </si>
   <si>
@@ -876,12 +854,6 @@
     <t>reciben terapia farmacológica y asesoramiento para prevenir ataques cardíacos y ataques cerebrovasculares</t>
   </si>
   <si>
-    <t>Consejería de estilo de vida</t>
-  </si>
-  <si>
-    <t>consejos recibidos durante los últimos 12 meses por parte de un médico o profesional de la salud, entre toda la población</t>
-  </si>
-  <si>
     <t xml:space="preserve"> recibieron consejo de dejar de consumir tabaco o no comienzar</t>
   </si>
   <si>
@@ -906,39 +878,54 @@
     <t>Factores de riesgo múltiples</t>
   </si>
   <si>
-    <t>de la población tiene 3 a 5 factores de riesgo</t>
-  </si>
-  <si>
-    <t>de la población tiene 1 a 2 factores de riesgo</t>
-  </si>
-  <si>
-    <t>de la población tiene 0 factores de riesgo</t>
-  </si>
-  <si>
     <t>de la población 18-44 tiene 3 a 5 factores de riesgo</t>
   </si>
   <si>
     <t>de la población 45-69 tiene 3 a 5 factores de riesgo</t>
   </si>
   <si>
+    <t>de la population âgée de 18 à 69 ans ne présente aucun facteur de risque</t>
+  </si>
+  <si>
+    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque</t>
+  </si>
+  <si>
+    <t>de la population âgée de 18 à 69 ans présente 1 à 2 facteurs de risque</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 3 a 5 factores de riesgo</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 1 a 2 factores de riesgo</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 0 factores de riesgo</t>
+  </si>
+  <si>
+    <t>Consejería de estilo de vida*</t>
+  </si>
+  <si>
+    <t>*consejos recibidos durante los últimos 12 meses por parte de un médico o profesional de la salud, entre toda la población</t>
+  </si>
+  <si>
+    <t>* IMC ≥ 25</t>
+  </si>
+  <si>
+    <t>** IMC ≥ 30</t>
+  </si>
+  <si>
+    <t>* PAS ≥ 140 et/ou PAD ≥ 90 mmHg</t>
+  </si>
+  <si>
+    <t>* PAS ≥ 140 y/o PAD ≥ 90 mmHg</t>
+  </si>
+  <si>
     <t>* BMI ≥ 25</t>
   </si>
   <si>
     <t>** BMI ≥ 30</t>
   </si>
   <si>
-    <t>* IMC ≥ 25</t>
-  </si>
-  <si>
-    <t>** IMC ≥ 30</t>
-  </si>
-  <si>
-    <t>* PAS ≥ 140 y/o PAD ≥ 90 mmHg</t>
-  </si>
-  <si>
-    <t>* PAS ≥ 140 et/ou PAD ≥ 90 mmHg</t>
-  </si>
-  <si>
     <t>* SBP ≥ 140 and/or DBP ≥ 90 mmHg</t>
   </si>
   <si>
@@ -960,6 +947,51 @@
     <t>of the population are obese**</t>
   </si>
   <si>
+    <t>of the population have raised blood pressure* or are currently on medication for raised blood pressure</t>
+  </si>
+  <si>
+    <t>de la population souffre d'hypertension artérielle* ou prend actuellement des médicaments pour traiter l'hypertension</t>
+  </si>
+  <si>
+    <t>de la población tiene presión arterial elevada* o toma medicación para la presión arterial elevada</t>
+  </si>
+  <si>
+    <t>of the population have raised blood sugar* or are currently on medication for diabetes</t>
+  </si>
+  <si>
+    <t>de la population présente une glycémie élevée* ou prend actuellement des médicaments contre le diabète</t>
+  </si>
+  <si>
+    <t>de la población tiene la glucosa en sangre elevada* o está en tratamiento para diabetes</t>
+  </si>
+  <si>
+    <t>of the population have raised total cholesterol*</t>
+  </si>
+  <si>
+    <t>of men have low HDL (good cholesterol)**</t>
+  </si>
+  <si>
+    <t>of women have low HDL (good cholesterol)***</t>
+  </si>
+  <si>
+    <t>de la population présente un taux de cholestérol total élevé*</t>
+  </si>
+  <si>
+    <t>des hommes ont un faible taux de HDL (bon cholestérol)**</t>
+  </si>
+  <si>
+    <t>des femmes ont un faible taux de HDL (bon cholestérol)***</t>
+  </si>
+  <si>
+    <t>de la población tiene el colesterol total elevado*</t>
+  </si>
+  <si>
+    <t>de los hombres tienen bajo el colesterol HDL (colesterol bueno)**</t>
+  </si>
+  <si>
+    <t>de las mujeres tienen bajo el colesterol HDL (colesterol bueno)***</t>
+  </si>
+  <si>
     <t>de la population est en surpoids*</t>
   </si>
   <si>
@@ -972,49 +1004,274 @@
     <t>de la población tienen obesidad**</t>
   </si>
   <si>
+    <t>* current daily smoking, &lt;5 servings of fruit or vegetables per day, not meeting WHO recommendations for physical activity, BMI≥25, raised blood pressure (SBP ≥ 140 and/or DBP ≥ 90 mmHg or currently on medication)</t>
+  </si>
+  <si>
+    <t>Tobacco Use</t>
+  </si>
+  <si>
+    <t>of the population are current smokers</t>
+  </si>
+  <si>
+    <t>of men</t>
+  </si>
+  <si>
+    <t>of women</t>
+  </si>
+  <si>
+    <t>Among current smokers</t>
+  </si>
+  <si>
+    <t>smoke daily</t>
+  </si>
+  <si>
+    <t>smoke manufactured cigarettes</t>
+  </si>
+  <si>
+    <t>smoke hand-rolled cigarettes</t>
+  </si>
+  <si>
+    <t>smoke cigars, cheroots or cigarillos</t>
+  </si>
+  <si>
+    <t>smoke pipes</t>
+  </si>
+  <si>
+    <t>smoke shisha</t>
+  </si>
+  <si>
+    <t>have tried to stop smoking during the past 12 months</t>
+  </si>
+  <si>
+    <t>of the population are current smokeless users</t>
+  </si>
+  <si>
+    <t>of the population currently use any tobacco products</t>
+  </si>
+  <si>
+    <t>Alcohol Use</t>
+  </si>
+  <si>
+    <t>of the population are current drinkers</t>
+  </si>
+  <si>
+    <t>of 18-44 years</t>
+  </si>
+  <si>
+    <t>of 45-69 years</t>
+  </si>
+  <si>
+    <t>are current drinkers</t>
+  </si>
+  <si>
+    <t>of the population are lifetime abstainers</t>
+  </si>
+  <si>
+    <t>Heavy episodic drinking</t>
+  </si>
+  <si>
+    <t>of the population consumed 6 or more drinks on one occasion in the past 30 days</t>
+  </si>
+  <si>
+    <t>of men consumed 6 or more drinks on one occasion</t>
+  </si>
+  <si>
+    <t>of women consumed 6 or more drinks on one occasion</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t>mean number of days fruits are consumed in a typical week</t>
+  </si>
+  <si>
+    <t>mean number of days vegetables consumed in a typical week</t>
+  </si>
+  <si>
+    <t>of the population eat less than 5 servings of fruit and/or vegetables per day</t>
+  </si>
+  <si>
+    <t>of the population do not eat any fruit or vegetables</t>
+  </si>
+  <si>
+    <t>of the population always or often eat processed foods high in salt</t>
+  </si>
+  <si>
+    <t>mean number of grams of salt consumed per day</t>
+  </si>
+  <si>
+    <t>Physical Activity</t>
+  </si>
+  <si>
+    <t>of the population are not meeting WHO's recommendation for physical activity</t>
+  </si>
+  <si>
+    <t>Among women …</t>
+  </si>
+  <si>
+    <t>Among men …</t>
+  </si>
+  <si>
+    <t>are not meeting WHO's recommendation for physical activity</t>
+  </si>
+  <si>
+    <t>are not engaging in any vigorous physical activity</t>
+  </si>
+  <si>
+    <t>of the population do not do any work-related activity</t>
+  </si>
+  <si>
+    <t>of the population do not do any transport-related activity e.g. walking or cycling</t>
+  </si>
+  <si>
+    <t>of the population do not do any activity in their leisure time</t>
+  </si>
+  <si>
+    <t>Average time spent in sedentary activity per day</t>
+  </si>
+  <si>
+    <t>minutes</t>
+  </si>
+  <si>
+    <t>hours</t>
+  </si>
+  <si>
+    <t>Body Mass Index</t>
+  </si>
+  <si>
+    <t>of the population are overweight*</t>
+  </si>
+  <si>
+    <t>of men are overweight</t>
+  </si>
+  <si>
+    <t>of women are overweight</t>
+  </si>
+  <si>
+    <t>of the population are obese**</t>
+  </si>
+  <si>
+    <t>of men are obese</t>
+  </si>
+  <si>
+    <t>of women are obese</t>
+  </si>
+  <si>
+    <t>* BMI ≥ 25</t>
+  </si>
+  <si>
+    <t>** BMI ≥ 30</t>
+  </si>
+  <si>
+    <t>Raised Blood Pressure</t>
+  </si>
+  <si>
     <t>of the population have raised blood pressure* or are currently on medication for raised blood pressure</t>
   </si>
   <si>
-    <t>de la population souffre d'hypertension artérielle* ou prend actuellement des médicaments pour traiter l'hypertension</t>
-  </si>
-  <si>
-    <t>de la población tiene presión arterial elevada* o toma medicación para la presión arterial elevada</t>
+    <t>Of those …</t>
+  </si>
+  <si>
+    <t>have been previously diagnosed with raised blood pressure (aware)</t>
+  </si>
+  <si>
+    <t>are taking medication for their raised blood pressure (treated)</t>
+  </si>
+  <si>
+    <t>have their blood pressure under control (controlled)</t>
+  </si>
+  <si>
+    <t>* SBP ≥ 140 and/or DBP ≥ 90 mmHg</t>
+  </si>
+  <si>
+    <t>Raised Blood Sugar</t>
   </si>
   <si>
     <t>of the population have raised blood sugar* or are currently on medication for diabetes</t>
   </si>
   <si>
-    <t>de la population présente une glycémie élevée* ou prend actuellement des médicaments contre le diabète</t>
-  </si>
-  <si>
-    <t>de la población tiene la glucosa en sangre elevada* o está en tratamiento para diabetes</t>
+    <t>are currently receiving treatment</t>
+  </si>
+  <si>
+    <t>of the population have never had their blood sugar measured</t>
+  </si>
+  <si>
+    <t>* ≥ 126 mg/dl</t>
+  </si>
+  <si>
+    <t>Raised Total Cholesterol</t>
   </si>
   <si>
     <t>of the population have raised total cholesterol*</t>
   </si>
   <si>
-    <t>de la population présente un taux de cholestérol total élevé*</t>
-  </si>
-  <si>
-    <t>de la población tiene el colesterol total elevado*</t>
-  </si>
-  <si>
     <t>of men have low HDL (good cholesterol)**</t>
   </si>
   <si>
-    <t>des hommes ont un faible taux de HDL (bon cholestérol)**</t>
-  </si>
-  <si>
-    <t>de los hombres tienen bajo el colesterol HDL (colesterol bueno)**</t>
-  </si>
-  <si>
     <t>of women have low HDL (good cholesterol)***</t>
   </si>
   <si>
-    <t>des femmes ont un faible taux de HDL (bon cholestérol)***</t>
-  </si>
-  <si>
-    <t>de las mujeres tienen bajo el colesterol HDL (colesterol bueno)***</t>
+    <t>** &lt; 40 mg/d</t>
+  </si>
+  <si>
+    <t>*** &lt; 50 mg/d</t>
+  </si>
+  <si>
+    <t>Cardiovascular Disease</t>
+  </si>
+  <si>
+    <t>of the population aged 40-69 years have a 10-year CVD risk ≥20% or have existing CVD</t>
+  </si>
+  <si>
+    <t>of which</t>
+  </si>
+  <si>
+    <t>are receiving drug therapy and counselling to prevent heart attacks and strokes</t>
+  </si>
+  <si>
+    <t>Lifestyle Advice*</t>
+  </si>
+  <si>
+    <t>* advice received in the past 12 months from a health worker, among the total population</t>
+  </si>
+  <si>
+    <t>were advised to quit smoking or not start</t>
+  </si>
+  <si>
+    <t>were advised to lower the salt content in their food</t>
+  </si>
+  <si>
+    <t>were advised to eat at least five portions of fruit and vegetables a day</t>
+  </si>
+  <si>
+    <t>were advised to reduce fat in their diet</t>
+  </si>
+  <si>
+    <t>were advised to do more physical activity</t>
+  </si>
+  <si>
+    <t>were advised to maintain healthy weight/lose weight</t>
+  </si>
+  <si>
+    <t>were advised to reduce sugary drinks</t>
+  </si>
+  <si>
+    <t>Multiple Risk Factors</t>
+  </si>
+  <si>
+    <t>of the population aged 18-69 have 3 to 5 risk factors</t>
+  </si>
+  <si>
+    <t>of the population aged 18-69 have 1 to 2 risk factors</t>
+  </si>
+  <si>
+    <t>of the population aged 18-69 have 0 risk factors</t>
+  </si>
+  <si>
+    <t>of 18-44 year olds have 3 to 5 risk factors</t>
+  </si>
+  <si>
+    <t>of 45-69 year olds have 3 to 5 risk factors</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1120,9 +1377,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1439,7 +1693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.875" customWidth="1"/>
@@ -1454,26 +1708,26 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>329</v>
       </c>
       <c r="D3">
         <v>9.5868345383227305E-2</v>
@@ -1481,13 +1735,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>2</v>
+        <v>330</v>
       </c>
       <c r="D4">
         <v>0.16904970534544</v>
@@ -1495,13 +1749,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>3</v>
+        <v>331</v>
       </c>
       <c r="D5">
         <v>2.8757018116263501E-2</v>
@@ -1509,18 +1763,18 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>39</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>333</v>
       </c>
       <c r="D7">
         <v>0.292629104874292</v>
@@ -1528,13 +1782,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>334</v>
       </c>
       <c r="D8">
         <v>0.86677187571240999</v>
@@ -1542,13 +1796,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>335</v>
       </c>
       <c r="D9">
         <v>7.20366105350949E-2</v>
@@ -1556,13 +1810,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>336</v>
       </c>
       <c r="D10">
         <v>2.46664092701823E-3</v>
@@ -1570,13 +1824,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>337</v>
       </c>
       <c r="D11">
         <v>1.36202893634498E-2</v>
@@ -1584,13 +1838,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>338</v>
       </c>
       <c r="D12">
         <v>7.9274449407799995E-3</v>
@@ -1598,13 +1852,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>4</v>
+        <v>339</v>
       </c>
       <c r="D13">
         <v>0.54865878663552003</v>
@@ -1612,13 +1866,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D14">
         <v>0.47170403520997101</v>
@@ -1626,13 +1880,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>99</v>
+        <v>340</v>
       </c>
       <c r="D15">
         <v>1.6642277782832301E-3</v>
@@ -1640,13 +1894,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>103</v>
+        <v>341</v>
       </c>
       <c r="D16">
         <v>9.6711699166281195E-2</v>
@@ -1654,18 +1908,18 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
-        <v>5</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>343</v>
       </c>
       <c r="D19">
         <v>0.27081665048940201</v>
@@ -1673,13 +1927,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2</v>
+        <v>330</v>
       </c>
       <c r="D20">
         <v>0.35574847314701302</v>
@@ -1687,13 +1941,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>3</v>
+        <v>331</v>
       </c>
       <c r="D21">
         <v>0.19292950376874901</v>
@@ -1701,13 +1955,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>6</v>
+        <v>344</v>
       </c>
       <c r="D22">
         <v>0.31072667276911098</v>
@@ -1715,13 +1969,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>7</v>
+        <v>345</v>
       </c>
       <c r="D23">
         <v>0.224325013535698</v>
@@ -1729,18 +1983,18 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
-        <v>106</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>347</v>
       </c>
       <c r="D25">
         <v>0.137924315803339</v>
@@ -1748,18 +2002,18 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C26" s="6" t="s">
-        <v>107</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>108</v>
+        <v>349</v>
       </c>
       <c r="D27">
         <v>8.1187097871824696E-2</v>
@@ -1767,13 +2021,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>9</v>
+        <v>350</v>
       </c>
       <c r="D28">
         <v>0.12946420130368799</v>
@@ -1781,13 +2035,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>10</v>
+        <v>351</v>
       </c>
       <c r="D29">
         <v>3.6897568473613002E-2</v>
@@ -1795,23 +2049,23 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C31" s="2" t="s">
-        <v>11</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C32" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>86</v>
+        <v>353</v>
       </c>
       <c r="D33">
         <v>3.1231828612839099</v>
@@ -1819,13 +2073,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>87</v>
+        <v>354</v>
       </c>
       <c r="D34">
         <v>3.8263976641185198</v>
@@ -1833,13 +2087,13 @@
     </row>
     <row r="35" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>12</v>
+        <v>355</v>
       </c>
       <c r="D35">
         <v>0.91927039010522005</v>
@@ -1847,13 +2101,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>13</v>
+        <v>356</v>
       </c>
       <c r="D36">
         <v>0.26345796430082002</v>
@@ -1861,13 +2115,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>110</v>
+        <v>357</v>
       </c>
       <c r="D37">
         <v>0.410590091993219</v>
@@ -1875,13 +2129,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>112</v>
+        <v>358</v>
       </c>
       <c r="D38">
         <v>4.5</v>
@@ -1889,18 +2143,18 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C40" s="2" t="s">
-        <v>14</v>
+        <v>359</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>113</v>
+        <v>360</v>
       </c>
       <c r="D41">
         <v>0.15331747397770601</v>
@@ -1908,23 +2162,23 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C42" s="7" t="s">
-        <v>114</v>
+        <v>361</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C43" s="7" t="s">
-        <v>115</v>
+        <v>362</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>116</v>
+        <v>363</v>
       </c>
       <c r="D44">
         <v>0.126894667688952</v>
@@ -1932,13 +2186,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>116</v>
+        <v>363</v>
       </c>
       <c r="D45">
         <v>0.17937866963428001</v>
@@ -1946,13 +2200,13 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>117</v>
+        <v>364</v>
       </c>
       <c r="D46">
         <v>0.230499947806418</v>
@@ -1960,13 +2214,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>117</v>
+        <v>364</v>
       </c>
       <c r="D47">
         <v>0.57438181124198595</v>
@@ -1974,13 +2228,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>118</v>
+        <v>365</v>
       </c>
       <c r="D48">
         <v>0.26689826575900999</v>
@@ -1988,13 +2242,13 @@
     </row>
     <row r="49" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>119</v>
+        <v>366</v>
       </c>
       <c r="D49">
         <v>0.73627233813542403</v>
@@ -2002,13 +2256,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>120</v>
+        <v>367</v>
       </c>
       <c r="D50">
         <v>0.431924632566349</v>
@@ -2016,13 +2270,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>121</v>
+        <v>368</v>
       </c>
       <c r="D51">
         <v>234.98297636691001</v>
@@ -2030,28 +2284,28 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C52" s="7" t="s">
-        <v>122</v>
+        <v>369</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C53" s="7" t="s">
-        <v>123</v>
+        <v>370</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
-        <v>15</v>
+        <v>371</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>306</v>
+        <v>372</v>
       </c>
       <c r="D56">
         <v>0.70431390646202996</v>
@@ -2059,13 +2313,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>19</v>
+        <v>373</v>
       </c>
       <c r="D57">
         <v>0.65998481314155899</v>
@@ -2073,13 +2327,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>18</v>
+        <v>374</v>
       </c>
       <c r="D58">
         <v>0.74541050844360002</v>
@@ -2087,13 +2341,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="D59">
         <v>0.31361173699675299</v>
@@ -2101,13 +2355,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>17</v>
+        <v>376</v>
       </c>
       <c r="D60">
         <v>0.233490002268708</v>
@@ -2115,42 +2369,42 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>16</v>
+        <v>377</v>
       </c>
       <c r="D61">
         <v>0.38789096979522403</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C62" s="7" t="s">
-        <v>295</v>
+      <c r="C62" s="3" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C63" s="7" t="s">
-        <v>296</v>
+      <c r="C63" s="3" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C65" s="2" t="s">
-        <v>20</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>312</v>
+        <v>381</v>
       </c>
       <c r="D66">
         <v>0.36225792037284199</v>
@@ -2158,18 +2412,18 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C67" s="7" t="s">
-        <v>124</v>
+        <v>382</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>125</v>
+        <v>383</v>
       </c>
       <c r="D68">
         <v>0.61052311680398197</v>
@@ -2177,13 +2431,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>126</v>
+        <v>384</v>
       </c>
       <c r="D69">
         <v>0.40527095734318003</v>
@@ -2191,21 +2445,21 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B70" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>127</v>
+        <v>385</v>
       </c>
       <c r="D70">
         <v>0.17892397607586299</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C71" s="7" t="s">
-        <v>301</v>
+      <c r="C71" s="3" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2213,18 +2467,18 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C73" s="2" t="s">
-        <v>21</v>
+        <v>387</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B74" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>315</v>
+        <v>388</v>
       </c>
       <c r="D74">
         <v>0.32595983575895299</v>
@@ -2232,13 +2486,13 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>129</v>
+        <v>389</v>
       </c>
       <c r="D75">
         <v>0.490675199259967</v>
@@ -2246,21 +2500,21 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="D76">
         <v>0.150429409241252</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="10" t="s">
-        <v>302</v>
+      <c r="C77" s="7" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2268,18 +2522,18 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C79" s="2" t="s">
-        <v>22</v>
+        <v>392</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="B80" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>318</v>
+        <v>393</v>
       </c>
       <c r="D80">
         <v>0.30846405700899199</v>
@@ -2287,13 +2541,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B81" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>321</v>
+        <v>394</v>
       </c>
       <c r="D81">
         <v>0.51068816005975304</v>
@@ -2301,13 +2555,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B82" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>324</v>
+        <v>395</v>
       </c>
       <c r="D82">
         <v>0.661777413579962</v>
@@ -2315,36 +2569,36 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="8"/>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="7" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8"/>
-      <c r="C84" s="10" t="s">
-        <v>304</v>
+      <c r="C84" s="7" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="8"/>
-      <c r="C85" s="10" t="s">
-        <v>305</v>
+      <c r="C85" s="7" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C87" s="2" t="s">
-        <v>23</v>
+        <v>398</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B88" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>133</v>
+        <v>399</v>
       </c>
       <c r="D88">
         <v>0.13926036430897001</v>
@@ -2352,18 +2606,18 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C89" s="7" t="s">
-        <v>134</v>
+        <v>400</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>135</v>
+        <v>401</v>
       </c>
       <c r="D90">
         <v>0.43903233005354497</v>
@@ -2371,23 +2625,23 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C92" s="2" t="s">
-        <v>136</v>
+        <v>402</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="7" t="s">
-        <v>137</v>
+        <v>403</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B94" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>138</v>
+        <v>404</v>
       </c>
       <c r="D94">
         <v>0.11646196157246599</v>
@@ -2395,13 +2649,13 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>141</v>
+        <v>405</v>
       </c>
       <c r="D95">
         <v>0.28036732652075302</v>
@@ -2409,13 +2663,13 @@
     </row>
     <row r="96" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B96" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>139</v>
+        <v>406</v>
       </c>
       <c r="D96">
         <v>0.36463313156733501</v>
@@ -2423,13 +2677,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B97" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>142</v>
+        <v>407</v>
       </c>
       <c r="D97">
         <v>0.38542192812346798</v>
@@ -2437,13 +2691,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B98" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>143</v>
+        <v>408</v>
       </c>
       <c r="D98">
         <v>0.44257002102835402</v>
@@ -2451,13 +2705,13 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B99" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>144</v>
+        <v>409</v>
       </c>
       <c r="D99">
         <v>0.46108059865707801</v>
@@ -2465,13 +2719,13 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B100" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>140</v>
+        <v>410</v>
       </c>
       <c r="D100">
         <v>0.41747082475470298</v>
@@ -2479,18 +2733,18 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C102" s="2" t="s">
-        <v>24</v>
+        <v>411</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B103" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>145</v>
+        <v>412</v>
       </c>
       <c r="D103">
         <v>0.27102306775179902</v>
@@ -2498,13 +2752,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B104" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>146</v>
+        <v>413</v>
       </c>
       <c r="D104">
         <v>0.714768272466904</v>
@@ -2512,13 +2766,13 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B105" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>25</v>
+        <v>414</v>
       </c>
       <c r="D105">
         <v>1.4208659782986801E-2</v>
@@ -2526,13 +2780,13 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B106" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>147</v>
+        <v>415</v>
       </c>
       <c r="D106">
         <v>0.17272484176882499</v>
@@ -2540,16 +2794,21 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B107" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>148</v>
+        <v>416</v>
       </c>
       <c r="D107">
         <v>0.38490777169469598</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C108" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -2570,35 +2829,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>27</v>
-      </c>
       <c r="C1" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2606,10 +2865,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2617,87 +2876,87 @@
         <v>3</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2705,43 +2964,43 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2749,21 +3008,21 @@
         <v>5</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,10 +3030,10 @@
         <v>2</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,10 +3041,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2793,10 +3052,10 @@
         <v>6</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2804,21 +3063,21 @@
         <v>7</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2826,32 +3085,32 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2859,10 +3118,10 @@
         <v>9</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2870,10 +3129,10 @@
         <v>10</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2881,43 +3140,43 @@
         <v>11</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2925,10 +3184,10 @@
         <v>12</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2936,32 +3195,32 @@
         <v>13</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2969,153 +3228,153 @@
         <v>14</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -3123,10 +3382,10 @@
         <v>15</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -3134,10 +3393,10 @@
         <v>306</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3145,10 +3404,10 @@
         <v>19</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3156,10 +3415,10 @@
         <v>18</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3167,10 +3426,10 @@
         <v>307</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3178,10 +3437,10 @@
         <v>17</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3189,32 +3448,32 @@
         <v>16</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="10" t="s">
+      <c r="A62" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B62" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>297</v>
-      </c>
       <c r="C62" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="10" t="s">
+      <c r="A63" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B63" s="7" t="s">
-        <v>298</v>
-      </c>
       <c r="C63" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3222,76 +3481,76 @@
         <v>20</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="3" t="s">
         <v>301</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3304,53 +3563,53 @@
         <v>21</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="7" t="s">
         <v>302</v>
       </c>
     </row>
@@ -3364,18 +3623,18 @@
         <v>22</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>320</v>
@@ -3383,56 +3642,56 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>321</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="7" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="7" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C85" s="10" t="s">
+      <c r="C85" s="7" t="s">
         <v>305</v>
       </c>
     </row>
@@ -3441,142 +3700,142 @@
         <v>23</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3584,18 +3843,18 @@
         <v>24</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>145</v>
+        <v>210</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>208</v>
+        <v>288</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>290</v>
@@ -3603,10 +3862,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>209</v>
+        <v>289</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>291</v>
@@ -3614,10 +3873,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>25</v>
+        <v>211</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>292</v>
@@ -3625,24 +3884,24 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/STEPS_data_analysis/templates/data_fromR.xlsx
+++ b/STEPS_data_analysis/templates/data_fromR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\Latest from Lucas\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\most recent from Lucas\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3838ED49-21FF-4DB5-A83E-601E275F168B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8578DA14-80C9-4806-8D7A-1970FAFD9B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="345" windowWidth="20370" windowHeight="14670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="416">
   <si>
     <t>ind_level</t>
   </si>
@@ -653,9 +653,6 @@
     <t>bm1l1</t>
   </si>
   <si>
-    <t>of the population aged 18-69 have 3 to 5 risk factors</t>
-  </si>
-  <si>
     <t>of the population aged 18-69 have 0 risk factors</t>
   </si>
   <si>
@@ -887,15 +884,9 @@
     <t>de la population âgée de 18 à 69 ans ne présente aucun facteur de risque</t>
   </si>
   <si>
-    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque</t>
-  </si>
-  <si>
     <t>de la population âgée de 18 à 69 ans présente 1 à 2 facteurs de risque</t>
   </si>
   <si>
-    <t>de la población 18-69 tiene 3 a 5 factores de riesgo</t>
-  </si>
-  <si>
     <t>de la población 18-69 tiene 1 a 2 factores de riesgo</t>
   </si>
   <si>
@@ -1007,6 +998,9 @@
     <t>* current daily smoking, &lt;5 servings of fruit or vegetables per day, not meeting WHO recommendations for physical activity, BMI≥25, raised blood pressure (SBP ≥ 140 and/or DBP ≥ 90 mmHg or currently on medication)</t>
   </si>
   <si>
+    <t>of the population aged 18-69 have 3 to 5 risk factors*</t>
+  </si>
+  <si>
     <t>Tobacco Use</t>
   </si>
   <si>
@@ -1259,9 +1253,6 @@
     <t>Multiple Risk Factors</t>
   </si>
   <si>
-    <t>of the population aged 18-69 have 3 to 5 risk factors</t>
-  </si>
-  <si>
     <t>of the population aged 18-69 have 1 to 2 risk factors</t>
   </si>
   <si>
@@ -1272,6 +1263,12 @@
   </si>
   <si>
     <t>of 45-69 year olds have 3 to 5 risk factors</t>
+  </si>
+  <si>
+    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque*</t>
+  </si>
+  <si>
+    <t>de la población 18-69 tiene 3 a 5 factores de riesgo*</t>
   </si>
 </sst>
 </file>
@@ -1716,7 +1713,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C2" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -1727,10 +1724,10 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D3">
-        <v>9.5868345383227305E-2</v>
+        <v>0.160364682044464</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -1741,10 +1738,10 @@
         <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D4">
-        <v>0.16904970534544</v>
+        <v>0.30907395604458199</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1755,15 +1752,15 @@
         <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D5">
-        <v>2.8757018116263501E-2</v>
+        <v>1.8779530695897401E-2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1774,10 +1771,10 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D7">
-        <v>0.292629104874292</v>
+        <v>0.70570621985556903</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1788,10 +1785,10 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D8">
-        <v>0.86677187571240999</v>
+        <v>0.76449163359847805</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1802,10 +1799,10 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D9">
-        <v>7.20366105350949E-2</v>
+        <v>0.44839841691918603</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1816,10 +1813,10 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D10">
-        <v>2.46664092701823E-3</v>
+        <v>5.4807414922094497E-2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1830,10 +1827,10 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D11">
-        <v>1.36202893634498E-2</v>
+        <v>4.7524175058262799E-2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1844,10 +1841,10 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D12">
-        <v>7.9274449407799995E-3</v>
+        <v>2.4063560083243601E-2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1858,10 +1855,10 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D13">
-        <v>0.54865878663552003</v>
+        <v>0.55855780679192701</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1875,7 +1872,7 @@
         <v>104</v>
       </c>
       <c r="D14">
-        <v>0.47170403520997101</v>
+        <v>0.20770326276057099</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1886,10 +1883,10 @@
         <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D15">
-        <v>1.6642277782832301E-3</v>
+        <v>4.0118438104479598E-2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1900,15 +1897,15 @@
         <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D16">
-        <v>9.6711699166281195E-2</v>
+        <v>0.191695202301015</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C18" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1919,10 +1916,10 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D19">
-        <v>0.27081665048940201</v>
+        <v>0.24240730633786101</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -1933,10 +1930,10 @@
         <v>41</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D20">
-        <v>0.35574847314701302</v>
+        <v>0.37187823047679402</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -1947,10 +1944,10 @@
         <v>42</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="D21">
-        <v>0.19292950376874901</v>
+        <v>0.11913886495367999</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -1961,10 +1958,10 @@
         <v>50</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D22">
-        <v>0.31072667276911098</v>
+        <v>0.227451008208716</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1975,15 +1972,15 @@
         <v>51</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D23">
-        <v>0.224325013535698</v>
+        <v>0.29584119241205198</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1994,15 +1991,15 @@
         <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D25">
-        <v>0.137924315803339</v>
+        <v>0.56731498184623697</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C26" s="6" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2013,10 +2010,10 @@
         <v>40</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D27">
-        <v>8.1187097871824696E-2</v>
+        <v>6.4642014615840696E-2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2027,10 +2024,10 @@
         <v>41</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D28">
-        <v>0.12946420130368799</v>
+        <v>0.10125023746349</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2041,15 +2038,15 @@
         <v>42</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D29">
-        <v>3.6897568473613002E-2</v>
+        <v>3.0118539907071001E-2</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C31" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2065,10 +2062,10 @@
         <v>40</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D33">
-        <v>3.1231828612839099</v>
+        <v>1.9733104255718199</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2079,10 +2076,10 @@
         <v>40</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D34">
-        <v>3.8263976641185198</v>
+        <v>5.5808164494881396</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2093,10 +2090,10 @@
         <v>40</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D35">
-        <v>0.91927039010522005</v>
+        <v>0.87707033328213202</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2107,10 +2104,10 @@
         <v>40</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D36">
-        <v>0.26345796430082002</v>
+        <v>0.16523776899590401</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2121,10 +2118,10 @@
         <v>40</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D37">
-        <v>0.410590091993219</v>
+        <v>4.9283122385275699E-2</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2135,15 +2132,15 @@
         <v>40</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="D38">
-        <v>4.5</v>
+        <v>7.42627600629294</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C40" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2154,20 +2151,20 @@
         <v>40</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D41">
-        <v>0.15331747397770601</v>
+        <v>6.8146896791999298E-2</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C42" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C43" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2178,10 +2175,10 @@
         <v>41</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D44">
-        <v>0.126894667688952</v>
+        <v>4.9708111097132898E-2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2192,10 +2189,10 @@
         <v>42</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D45">
-        <v>0.17937866963428001</v>
+        <v>8.5491154426724905E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2206,10 +2203,10 @@
         <v>41</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D46">
-        <v>0.230499947806418</v>
+        <v>0.20661698105741799</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2220,10 +2217,10 @@
         <v>42</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D47">
-        <v>0.57438181124198595</v>
+        <v>0.46284121967160302</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2234,10 +2231,10 @@
         <v>40</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D48">
-        <v>0.26689826575900999</v>
+        <v>0.11077504365006</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2248,10 +2245,10 @@
         <v>40</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D49">
-        <v>0.73627233813542403</v>
+        <v>0.122701232200988</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2262,10 +2259,10 @@
         <v>40</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D50">
-        <v>0.431924632566349</v>
+        <v>0.69169229917404396</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2276,25 +2273,25 @@
         <v>40</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D51">
-        <v>234.98297636691001</v>
+        <v>206.694946184587</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C52" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C53" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C55" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -2305,10 +2302,10 @@
         <v>40</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D56">
-        <v>0.70431390646202996</v>
+        <v>0.23630604428581101</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2319,10 +2316,10 @@
         <v>41</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D57">
-        <v>0.65998481314155899</v>
+        <v>0.105112304071224</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -2333,10 +2330,10 @@
         <v>42</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D58">
-        <v>0.74541050844360002</v>
+        <v>0.36973349841307301</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -2347,10 +2344,10 @@
         <v>40</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D59">
-        <v>0.31361173699675299</v>
+        <v>8.1964098381982306E-2</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -2361,10 +2358,10 @@
         <v>41</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D60">
-        <v>0.233490002268708</v>
+        <v>2.0873158126311801E-2</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -2375,25 +2372,25 @@
         <v>42</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D61">
-        <v>0.38789096979522403</v>
+        <v>0.14409517850225101</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C62" s="3" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C63" s="3" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C65" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2404,15 +2401,15 @@
         <v>40</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="D66">
-        <v>0.36225792037284199</v>
+        <v>0.21187331175465299</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C67" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -2423,10 +2420,10 @@
         <v>40</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D68">
-        <v>0.61052311680398197</v>
+        <v>0.38865550558407402</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -2437,10 +2434,10 @@
         <v>40</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D69">
-        <v>0.40527095734318003</v>
+        <v>0.16852550281634701</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2451,15 +2448,15 @@
         <v>40</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D70">
-        <v>0.17892397607586299</v>
+        <v>4.8831745814857802E-2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C71" s="3" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -2467,7 +2464,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C73" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2478,10 +2475,10 @@
         <v>40</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D74">
-        <v>0.32595983575895299</v>
+        <v>4.3863841746137902E-2</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -2492,10 +2489,10 @@
         <v>40</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D75">
-        <v>0.490675199259967</v>
+        <v>9.0534845632515501E-2</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -2506,15 +2503,15 @@
         <v>40</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D76">
-        <v>0.150429409241252</v>
+        <v>0.86078554000146901</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C77" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -2522,7 +2519,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C79" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -2533,10 +2530,10 @@
         <v>40</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D80">
-        <v>0.30846405700899199</v>
+        <v>0.101816314964547</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2547,10 +2544,10 @@
         <v>41</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D81">
-        <v>0.51068816005975304</v>
+        <v>0.482396432723741</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2561,33 +2558,33 @@
         <v>42</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D82">
-        <v>0.661777413579962</v>
+        <v>0.66846316843403197</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="8"/>
       <c r="C83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="8"/>
       <c r="C84" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="8"/>
       <c r="C85" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C87" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2598,15 +2595,15 @@
         <v>40</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D88">
-        <v>0.13926036430897001</v>
+        <v>6.3792454461009604E-2</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C89" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2617,20 +2614,20 @@
         <v>40</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D90">
-        <v>0.43903233005354497</v>
+        <v>0.165245904068308</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C92" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -2641,10 +2638,10 @@
         <v>40</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D94">
-        <v>0.11646196157246599</v>
+        <v>8.9112186820229103E-2</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -2655,10 +2652,10 @@
         <v>40</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D95">
-        <v>0.28036732652075302</v>
+        <v>0.120329734411022</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2669,10 +2666,10 @@
         <v>40</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D96">
-        <v>0.36463313156733501</v>
+        <v>0.225051310926947</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2683,10 +2680,10 @@
         <v>40</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D97">
-        <v>0.38542192812346798</v>
+        <v>0.141283376763297</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2697,10 +2694,10 @@
         <v>40</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D98">
-        <v>0.44257002102835402</v>
+        <v>0.15966470170795699</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -2711,10 +2708,10 @@
         <v>40</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D99">
-        <v>0.46108059865707801</v>
+        <v>0.112900081914135</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2725,15 +2722,15 @@
         <v>40</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D100">
-        <v>0.41747082475470298</v>
+        <v>0.13351394828633001</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C102" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -2744,10 +2741,10 @@
         <v>40</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="D103">
-        <v>0.27102306775179902</v>
+        <v>0.12122441098593099</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -2758,10 +2755,10 @@
         <v>40</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D104">
-        <v>0.714768272466904</v>
+        <v>0.81133960092391599</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -2772,10 +2769,10 @@
         <v>40</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D105">
-        <v>1.4208659782986801E-2</v>
+        <v>6.7435988081675002E-2</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -2786,10 +2783,10 @@
         <v>50</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D106">
-        <v>0.17272484176882499</v>
+        <v>8.7547552177706198E-2</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2800,15 +2797,15 @@
         <v>51</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D107">
-        <v>0.38490777169469598</v>
+        <v>0.234572905806846</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C108" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -2835,7 +2832,7 @@
         <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -2846,7 +2843,7 @@
         <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2857,7 +2854,7 @@
         <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2868,7 +2865,7 @@
         <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2879,7 +2876,7 @@
         <v>149</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2890,7 +2887,7 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2901,7 +2898,7 @@
         <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2912,7 +2909,7 @@
         <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2923,7 +2920,7 @@
         <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2934,7 +2931,7 @@
         <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2945,7 +2942,7 @@
         <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -2956,7 +2953,7 @@
         <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2967,7 +2964,7 @@
         <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2978,7 +2975,7 @@
         <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2989,7 +2986,7 @@
         <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -3000,7 +2997,7 @@
         <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -3011,7 +3008,7 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -3022,7 +3019,7 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -3033,7 +3030,7 @@
         <v>148</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -3044,7 +3041,7 @@
         <v>149</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -3055,7 +3052,7 @@
         <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3066,7 +3063,7 @@
         <v>162</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -3077,7 +3074,7 @@
         <v>163</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -3088,7 +3085,7 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3099,7 +3096,7 @@
         <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3110,7 +3107,7 @@
         <v>165</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -3121,7 +3118,7 @@
         <v>166</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -3132,7 +3129,7 @@
         <v>167</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3143,7 +3140,7 @@
         <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3154,7 +3151,7 @@
         <v>169</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -3165,7 +3162,7 @@
         <v>170</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -3176,7 +3173,7 @@
         <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3187,7 +3184,7 @@
         <v>172</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -3198,7 +3195,7 @@
         <v>173</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3209,7 +3206,7 @@
         <v>174</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -3220,7 +3217,7 @@
         <v>175</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -3231,7 +3228,7 @@
         <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3242,7 +3239,7 @@
         <v>176</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -3253,7 +3250,7 @@
         <v>177</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -3264,7 +3261,7 @@
         <v>178</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -3275,7 +3272,7 @@
         <v>179</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -3286,7 +3283,7 @@
         <v>179</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -3297,7 +3294,7 @@
         <v>180</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -3308,7 +3305,7 @@
         <v>180</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -3319,7 +3316,7 @@
         <v>181</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3330,7 +3327,7 @@
         <v>182</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -3341,7 +3338,7 @@
         <v>183</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -3352,7 +3349,7 @@
         <v>184</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3363,7 +3360,7 @@
         <v>121</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -3374,7 +3371,7 @@
         <v>185</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -3385,18 +3382,18 @@
         <v>30</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3407,7 +3404,7 @@
         <v>34</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3418,18 +3415,18 @@
         <v>33</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3440,7 +3437,7 @@
         <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3451,29 +3448,29 @@
         <v>31</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3484,18 +3481,18 @@
         <v>186</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3506,7 +3503,7 @@
         <v>187</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="68" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3517,7 +3514,7 @@
         <v>188</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3528,7 +3525,7 @@
         <v>189</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3539,18 +3536,18 @@
         <v>190</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3566,18 +3563,18 @@
         <v>191</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3588,7 +3585,7 @@
         <v>192</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3599,18 +3596,18 @@
         <v>193</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3626,73 +3623,73 @@
         <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B80" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="C80" s="7" t="s">
         <v>317</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="B81" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="C81" s="7" t="s">
         <v>318</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B82" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="C82" s="7" t="s">
         <v>319</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3703,7 +3700,7 @@
         <v>36</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3714,7 +3711,7 @@
         <v>194</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3725,7 +3722,7 @@
         <v>82</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3736,7 +3733,7 @@
         <v>195</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3747,7 +3744,7 @@
         <v>196</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3758,7 +3755,7 @@
         <v>197</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3769,7 +3766,7 @@
         <v>198</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,7 +3777,7 @@
         <v>201</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -3791,7 +3788,7 @@
         <v>199</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3802,7 +3799,7 @@
         <v>202</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3813,7 +3810,7 @@
         <v>203</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3824,7 +3821,7 @@
         <v>204</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3835,7 +3832,7 @@
         <v>200</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3846,40 +3843,40 @@
         <v>37</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>210</v>
+        <v>325</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>288</v>
+        <v>414</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>290</v>
+        <v>415</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3890,7 +3887,7 @@
         <v>205</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3901,7 +3898,7 @@
         <v>206</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/STEPS_data_analysis/templates/data_fromR.xlsx
+++ b/STEPS_data_analysis/templates/data_fromR.xlsx
@@ -1,27 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\R\most recent from Lucas\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8578DA14-80C9-4806-8D7A-1970FAFD9B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="345" windowWidth="20370" windowHeight="14670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="data" sheetId="1" r:id="rId1"/>
-    <sheet name="languages" sheetId="2" r:id="rId2"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="languages" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="418">
   <si>
     <t>ind_level</t>
   </si>
@@ -653,6 +646,9 @@
     <t>bm1l1</t>
   </si>
   <si>
+    <t>of the population aged 18-69 have 3 to 5 risk factors</t>
+  </si>
+  <si>
     <t>of the population aged 18-69 have 0 risk factors</t>
   </si>
   <si>
@@ -884,9 +880,15 @@
     <t>de la population âgée de 18 à 69 ans ne présente aucun facteur de risque</t>
   </si>
   <si>
+    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque</t>
+  </si>
+  <si>
     <t>de la population âgée de 18 à 69 ans présente 1 à 2 facteurs de risque</t>
   </si>
   <si>
+    <t>de la población 18-69 tiene 3 a 5 factores de riesgo</t>
+  </si>
+  <si>
     <t>de la población 18-69 tiene 1 a 2 factores de riesgo</t>
   </si>
   <si>
@@ -1001,281 +1003,279 @@
     <t>of the population aged 18-69 have 3 to 5 risk factors*</t>
   </si>
   <si>
-    <t>Tobacco Use</t>
-  </si>
-  <si>
-    <t>of the population are current smokers</t>
-  </si>
-  <si>
-    <t>of men</t>
-  </si>
-  <si>
-    <t>of women</t>
-  </si>
-  <si>
-    <t>Among current smokers</t>
-  </si>
-  <si>
-    <t>smoke daily</t>
-  </si>
-  <si>
-    <t>smoke manufactured cigarettes</t>
-  </si>
-  <si>
-    <t>smoke hand-rolled cigarettes</t>
-  </si>
-  <si>
-    <t>smoke cigars, cheroots or cigarillos</t>
-  </si>
-  <si>
-    <t>smoke pipes</t>
-  </si>
-  <si>
-    <t>smoke shisha</t>
-  </si>
-  <si>
-    <t>have tried to stop smoking during the past 12 months</t>
-  </si>
-  <si>
-    <t>of the population are current smokeless users</t>
-  </si>
-  <si>
-    <t>of the population currently use any tobacco products</t>
-  </si>
-  <si>
-    <t>Alcohol Use</t>
-  </si>
-  <si>
-    <t>of the population are current drinkers</t>
-  </si>
-  <si>
-    <t>of 18-44 years</t>
-  </si>
-  <si>
-    <t>of 45-69 years</t>
-  </si>
-  <si>
-    <t>are current drinkers</t>
-  </si>
-  <si>
-    <t>of the population are lifetime abstainers</t>
-  </si>
-  <si>
-    <t>Heavy episodic drinking</t>
-  </si>
-  <si>
-    <t>of the population consumed 6 or more drinks on one occasion in the past 30 days</t>
-  </si>
-  <si>
-    <t>of men consumed 6 or more drinks on one occasion</t>
-  </si>
-  <si>
-    <t>of women consumed 6 or more drinks on one occasion</t>
-  </si>
-  <si>
-    <t>Diet</t>
-  </si>
-  <si>
-    <t>mean number of days fruits are consumed in a typical week</t>
-  </si>
-  <si>
-    <t>mean number of days vegetables consumed in a typical week</t>
-  </si>
-  <si>
-    <t>of the population eat less than 5 servings of fruit and/or vegetables per day</t>
-  </si>
-  <si>
-    <t>of the population do not eat any fruit or vegetables</t>
-  </si>
-  <si>
-    <t>of the population always or often eat processed foods high in salt</t>
-  </si>
-  <si>
-    <t>mean number of grams of salt consumed per day</t>
-  </si>
-  <si>
-    <t>Physical Activity</t>
-  </si>
-  <si>
-    <t>of the population are not meeting WHO's recommendation for physical activity</t>
-  </si>
-  <si>
-    <t>Among women …</t>
-  </si>
-  <si>
-    <t>Among men …</t>
-  </si>
-  <si>
-    <t>are not meeting WHO's recommendation for physical activity</t>
-  </si>
-  <si>
-    <t>are not engaging in any vigorous physical activity</t>
-  </si>
-  <si>
-    <t>of the population do not do any work-related activity</t>
-  </si>
-  <si>
-    <t>of the population do not do any transport-related activity e.g. walking or cycling</t>
-  </si>
-  <si>
-    <t>of the population do not do any activity in their leisure time</t>
-  </si>
-  <si>
-    <t>Average time spent in sedentary activity per day</t>
-  </si>
-  <si>
-    <t>minutes</t>
-  </si>
-  <si>
-    <t>hours</t>
-  </si>
-  <si>
-    <t>Body Mass Index</t>
-  </si>
-  <si>
-    <t>of the population are overweight*</t>
-  </si>
-  <si>
-    <t>of men are overweight</t>
-  </si>
-  <si>
-    <t>of women are overweight</t>
-  </si>
-  <si>
-    <t>of the population are obese**</t>
-  </si>
-  <si>
-    <t>of men are obese</t>
-  </si>
-  <si>
-    <t>of women are obese</t>
-  </si>
-  <si>
-    <t>* BMI ≥ 25</t>
-  </si>
-  <si>
-    <t>** BMI ≥ 30</t>
-  </si>
-  <si>
-    <t>Raised Blood Pressure</t>
-  </si>
-  <si>
-    <t>of the population have raised blood pressure* or are currently on medication for raised blood pressure</t>
-  </si>
-  <si>
-    <t>Of those …</t>
-  </si>
-  <si>
-    <t>have been previously diagnosed with raised blood pressure (aware)</t>
-  </si>
-  <si>
-    <t>are taking medication for their raised blood pressure (treated)</t>
-  </si>
-  <si>
-    <t>have their blood pressure under control (controlled)</t>
-  </si>
-  <si>
-    <t>* SBP ≥ 140 and/or DBP ≥ 90 mmHg</t>
-  </si>
-  <si>
-    <t>Raised Blood Sugar</t>
-  </si>
-  <si>
-    <t>of the population have raised blood sugar* or are currently on medication for diabetes</t>
-  </si>
-  <si>
-    <t>are currently receiving treatment</t>
-  </si>
-  <si>
-    <t>of the population have never had their blood sugar measured</t>
-  </si>
-  <si>
-    <t>* ≥ 126 mg/dl</t>
-  </si>
-  <si>
-    <t>Raised Total Cholesterol</t>
-  </si>
-  <si>
-    <t>of the population have raised total cholesterol*</t>
-  </si>
-  <si>
-    <t>of men have low HDL (good cholesterol)**</t>
-  </si>
-  <si>
-    <t>of women have low HDL (good cholesterol)***</t>
-  </si>
-  <si>
-    <t>** &lt; 40 mg/d</t>
-  </si>
-  <si>
-    <t>*** &lt; 50 mg/d</t>
-  </si>
-  <si>
-    <t>Cardiovascular Disease</t>
-  </si>
-  <si>
-    <t>of the population aged 40-69 years have a 10-year CVD risk ≥20% or have existing CVD</t>
-  </si>
-  <si>
-    <t>of which</t>
-  </si>
-  <si>
-    <t>are receiving drug therapy and counselling to prevent heart attacks and strokes</t>
-  </si>
-  <si>
-    <t>Lifestyle Advice*</t>
-  </si>
-  <si>
-    <t>* advice received in the past 12 months from a health worker, among the total population</t>
-  </si>
-  <si>
-    <t>were advised to quit smoking or not start</t>
-  </si>
-  <si>
-    <t>were advised to lower the salt content in their food</t>
-  </si>
-  <si>
-    <t>were advised to eat at least five portions of fruit and vegetables a day</t>
-  </si>
-  <si>
-    <t>were advised to reduce fat in their diet</t>
-  </si>
-  <si>
-    <t>were advised to do more physical activity</t>
-  </si>
-  <si>
-    <t>were advised to maintain healthy weight/lose weight</t>
-  </si>
-  <si>
-    <t>were advised to reduce sugary drinks</t>
-  </si>
-  <si>
-    <t>Multiple Risk Factors</t>
-  </si>
-  <si>
-    <t>of the population aged 18-69 have 1 to 2 risk factors</t>
-  </si>
-  <si>
-    <t>of the population aged 18-69 have 0 risk factors</t>
-  </si>
-  <si>
-    <t>of 18-44 year olds have 3 to 5 risk factors</t>
-  </si>
-  <si>
-    <t>of 45-69 year olds have 3 to 5 risk factors</t>
-  </si>
-  <si>
-    <t>de la population âgée de 18 à 69 ans présente 3 à 5 facteurs de risque*</t>
-  </si>
-  <si>
-    <t>de la población 18-69 tiene 3 a 5 factores de riesgo*</t>
+    <t xml:space="preserve">Tobacco Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population are current smokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of women</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Among current smokers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoke daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoke manufactured cigarettes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoke hand-rolled cigarettes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoke cigars, cheroots or cigarillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoke pipes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">smoke shisha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">have tried to stop smoking during the past 12 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population are current smokeless users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population currently use any tobacco products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alcohol Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population are current drinkers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of 18-44 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of 45-69 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are current drinkers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population are lifetime abstainers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heavy episodic drinking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population consumed 6 or more drinks on one occasion in the past 30 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of men consumed 6 or more drinks on one occasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of women consumed 6 or more drinks on one occasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean number of days fruits are consumed in a typical week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean number of days vegetables consumed in a typical week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population eat less than 5 servings of fruit and/or vegetables per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population do not eat any fruit or vegetables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population always or often eat processed foods high in salt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean number of grams of salt consumed per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physical Activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population are not meeting WHO's recommendation for physical activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Among women …</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Among men …</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are not meeting WHO's recommendation for physical activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are not engaging in any vigorous physical activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population do not do any work-related activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population do not do any transport-related activity e.g. walking or cycling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population do not do any activity in their leisure time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average time spent in sedentary activity per day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Body Mass Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population are overweight*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of men are overweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of women are overweight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population are obese**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of men are obese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of women are obese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* BMI ≥ 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">** BMI ≥ 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raised Blood Pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population have raised blood pressure* or are currently on medication for raised blood pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Of those …</t>
+  </si>
+  <si>
+    <t xml:space="preserve">have been previously diagnosed with raised blood pressure (aware)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are taking medication for their raised blood pressure (treated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">have their blood pressure under control (controlled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* SBP ≥ 140 and/or DBP ≥ 90 mmHg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raised Blood Sugar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population have raised blood sugar* or are currently on medication for diabetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are currently receiving treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population have never had their blood sugar measured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* ≥ 126 mg/dl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raised Total Cholesterol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population have raised total cholesterol*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of men have low HDL (good cholesterol)**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of women have low HDL (good cholesterol)***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">** &lt; 40 mg/d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*** &lt; 50 mg/d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiovascular Disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population aged 40-69 years have a 10-year CVD risk ≥20% or have existing CVD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of which</t>
+  </si>
+  <si>
+    <t xml:space="preserve">are receiving drug therapy and counselling to prevent heart attacks and strokes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifestyle Advice*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* advice received in the past 12 months from a health worker, among the total population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">were advised to quit smoking or not start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">were advised to lower the salt content in their food</t>
+  </si>
+  <si>
+    <t xml:space="preserve">were advised to eat at least five portions of fruit and vegetables a day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">were advised to reduce fat in their diet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">were advised to do more physical activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">were advised to maintain healthy weight/lose weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">were advised to reduce sugary drinks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple Risk Factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population aged 18-69 have 3 to 5 risk factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population aged 18-69 have 1 to 2 risk factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of the population aged 18-69 have 0 risk factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of 18-44 year olds have 3 to 5 risk factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">of 45-69 year olds have 3 to 5 risk factors</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1284,12 +1284,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <b/>
     </font>
     <font>
       <sz val="12"/>
@@ -1303,7 +1303,14 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <b/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1315,14 +1322,7 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1689,15 +1689,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D108"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="3" max="3" width="58.625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="58.58203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1711,12 +1711,13 @@
         <v>208</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="C2" s="1" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+      <c r="D2"/>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>91</v>
       </c>
@@ -1724,13 +1725,13 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>327</v>
-      </c>
-      <c r="D3">
+        <v>330</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.160364682044464</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>91</v>
       </c>
@@ -1738,13 +1739,13 @@
         <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D4">
-        <v>0.30907395604458199</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.309073956044582</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -1752,18 +1753,19 @@
         <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="D5">
-        <v>1.8779530695897401E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.0187795306958974</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="C6" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>100</v>
       </c>
@@ -1771,13 +1773,13 @@
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D7">
-        <v>0.70570621985556903</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>334</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.705706219855569</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1785,13 +1787,13 @@
         <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>332</v>
-      </c>
-      <c r="D8">
-        <v>0.76449163359847805</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>335</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.764491633598478</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1799,13 +1801,13 @@
         <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>333</v>
-      </c>
-      <c r="D9">
-        <v>0.44839841691918603</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.448398416919186</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1813,13 +1815,13 @@
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>334</v>
-      </c>
-      <c r="D10">
-        <v>5.4807414922094497E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>337</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0548074149220945</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -1827,13 +1829,13 @@
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>335</v>
-      </c>
-      <c r="D11">
-        <v>4.7524175058262799E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.0475241750582628</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -1841,13 +1843,13 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>336</v>
-      </c>
-      <c r="D12">
-        <v>2.4063560083243601E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <v>339</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0240635600832436</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -1855,13 +1857,13 @@
         <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>337</v>
-      </c>
-      <c r="D13">
-        <v>0.55855780679192701</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.558557806791927</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -1871,11 +1873,11 @@
       <c r="C14" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D14">
-        <v>0.20770326276057099</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D14" t="n">
+        <v>0.207703262760571</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1883,13 +1885,13 @@
         <v>40</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D15">
-        <v>4.0118438104479598E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0401184381044796</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -1897,18 +1899,23 @@
         <v>40</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="D16">
+        <v>342</v>
+      </c>
+      <c r="D16" t="n">
         <v>0.191695202301015</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17">
+      <c r="C17"/>
+      <c r="D17"/>
+    </row>
+    <row r="18">
       <c r="C18" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1916,13 +1923,13 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>341</v>
-      </c>
-      <c r="D19">
-        <v>0.24240730633786101</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>344</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.242407306337861</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1930,13 +1937,13 @@
         <v>41</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="D20">
-        <v>0.37187823047679402</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.371878230476794</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1944,13 +1951,13 @@
         <v>42</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="D21">
-        <v>0.11913886495367999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>332</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.11913886495368</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -1958,13 +1965,13 @@
         <v>50</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="D22">
+        <v>345</v>
+      </c>
+      <c r="D22" t="n">
         <v>0.227451008208716</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>53</v>
       </c>
@@ -1972,18 +1979,19 @@
         <v>51</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="D23">
-        <v>0.29584119241205198</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.295841192412052</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="C24" s="6" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -1991,18 +1999,19 @@
         <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>345</v>
-      </c>
-      <c r="D25">
-        <v>0.56731498184623697</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>348</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.567314981846237</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="C26" s="6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+      <c r="D26"/>
+    </row>
+    <row r="27" ht="31" customHeight="1">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -2010,13 +2019,13 @@
         <v>40</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="D27">
-        <v>6.4642014615840696E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0646420146158407</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
         <v>55</v>
       </c>
@@ -2024,13 +2033,13 @@
         <v>41</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="D28">
+        <v>351</v>
+      </c>
+      <c r="D28" t="n">
         <v>0.10125023746349</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -2038,23 +2047,29 @@
         <v>42</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="D29">
-        <v>3.0118539907071001E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.030118539907071</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30"/>
+      <c r="D30"/>
+    </row>
+    <row r="31">
       <c r="C31" s="2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32">
       <c r="C32" s="7" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D32"/>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -2062,13 +2077,13 @@
         <v>40</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="D33">
-        <v>1.9733104255718199</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>354</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.97331042557182</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
         <v>57</v>
       </c>
@@ -2076,13 +2091,13 @@
         <v>40</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="D34">
-        <v>5.5808164494881396</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+      <c r="D34" t="n">
+        <v>5.58081644948814</v>
+      </c>
+    </row>
+    <row r="35" ht="31" customHeight="1">
       <c r="A35" t="s">
         <v>58</v>
       </c>
@@ -2090,13 +2105,13 @@
         <v>40</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="D35">
-        <v>0.87707033328213202</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+        <v>356</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.877070333282132</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -2104,13 +2119,13 @@
         <v>40</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="D36">
-        <v>0.16523776899590401</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.165237768995904</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
         <v>60</v>
       </c>
@@ -2118,13 +2133,13 @@
         <v>40</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="D37">
-        <v>4.9283122385275699E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>358</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0492831223852757</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -2132,18 +2147,23 @@
         <v>40</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="D38">
+        <v>359</v>
+      </c>
+      <c r="D38" t="n">
         <v>7.42627600629294</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39">
+      <c r="C39"/>
+      <c r="D39"/>
+    </row>
+    <row r="40">
       <c r="C40" s="2" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="D40"/>
+    </row>
+    <row r="41" ht="31" customHeight="1">
       <c r="A41" t="s">
         <v>61</v>
       </c>
@@ -2151,23 +2171,25 @@
         <v>40</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="D41">
-        <v>6.8146896791999298E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0681468967919993</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="C42" s="7" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43">
       <c r="C43" s="7" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44">
       <c r="A44" t="s">
         <v>61</v>
       </c>
@@ -2175,13 +2197,13 @@
         <v>41</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D44">
-        <v>4.9708111097132898E-2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.0497081110971329</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -2189,13 +2211,13 @@
         <v>42</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="D45">
-        <v>8.5491154426724905E-2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>364</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.0854911544267249</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -2203,13 +2225,13 @@
         <v>41</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="D46">
-        <v>0.20661698105741799</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.206616981057418</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="s">
         <v>62</v>
       </c>
@@ -2217,13 +2239,13 @@
         <v>42</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="D47">
-        <v>0.46284121967160302</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>365</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.462841219671603</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="s">
         <v>63</v>
       </c>
@@ -2231,13 +2253,13 @@
         <v>40</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="D48">
+        <v>366</v>
+      </c>
+      <c r="D48" t="n">
         <v>0.11077504365006</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="31" customHeight="1">
       <c r="A49" t="s">
         <v>64</v>
       </c>
@@ -2245,13 +2267,13 @@
         <v>40</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="D49">
+        <v>367</v>
+      </c>
+      <c r="D49" t="n">
         <v>0.122701232200988</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>65</v>
       </c>
@@ -2259,13 +2281,13 @@
         <v>40</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="D50">
-        <v>0.69169229917404396</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>368</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.691692299174044</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="s">
         <v>66</v>
       </c>
@@ -2273,28 +2295,35 @@
         <v>40</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="D51">
+        <v>369</v>
+      </c>
+      <c r="D51" t="n">
         <v>206.694946184587</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="C52" s="7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+      <c r="D52"/>
+    </row>
+    <row r="53">
       <c r="C53" s="7" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54">
+      <c r="C54"/>
+      <c r="D54"/>
+    </row>
+    <row r="55">
       <c r="C55" s="2" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>372</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56">
       <c r="A56" t="s">
         <v>68</v>
       </c>
@@ -2302,13 +2331,13 @@
         <v>40</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="D56">
-        <v>0.23630604428581101</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.236306044285811</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" t="s">
         <v>68</v>
       </c>
@@ -2316,13 +2345,13 @@
         <v>41</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="D57">
+        <v>374</v>
+      </c>
+      <c r="D57" t="n">
         <v>0.105112304071224</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>68</v>
       </c>
@@ -2330,13 +2359,13 @@
         <v>42</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="D58">
-        <v>0.36973349841307301</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.369733498413073</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" t="s">
         <v>67</v>
       </c>
@@ -2344,13 +2373,13 @@
         <v>40</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="D59">
-        <v>8.1964098381982306E-2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+        <v>376</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.0819640983819823</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -2358,13 +2387,13 @@
         <v>41</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="D60">
-        <v>2.0873158126311801E-2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.0208731581263118</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" t="s">
         <v>67</v>
       </c>
@@ -2372,28 +2401,35 @@
         <v>42</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="D61">
-        <v>0.14409517850225101</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+        <v>378</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.144095178502251</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="C62" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+        <v>379</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63">
       <c r="C63" s="3" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+        <v>380</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64">
+      <c r="C64"/>
+      <c r="D64"/>
+    </row>
+    <row r="65">
       <c r="C65" s="2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66" ht="31" customHeight="1">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -2401,18 +2437,19 @@
         <v>40</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="D66">
-        <v>0.21187331175465299</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+        <v>382</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.211873311754653</v>
+      </c>
+    </row>
+    <row r="67">
       <c r="C67" s="7" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+        <v>383</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -2420,13 +2457,13 @@
         <v>40</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="D68">
-        <v>0.38865550558407402</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+        <v>384</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.388655505584074</v>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -2434,13 +2471,13 @@
         <v>40</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="D69">
-        <v>0.16852550281634701</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+        <v>385</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.168525502816347</v>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -2448,26 +2485,29 @@
         <v>40</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="D70">
-        <v>4.8831745814857802E-2</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.0488317458148578</v>
+      </c>
+    </row>
+    <row r="71">
       <c r="C71" s="3" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+        <v>387</v>
+      </c>
+      <c r="D71"/>
+    </row>
+    <row r="72">
       <c r="C72" s="7"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D72"/>
+    </row>
+    <row r="73">
       <c r="C73" s="2" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+      <c r="D73"/>
+    </row>
+    <row r="74" ht="31" customHeight="1">
       <c r="A74" t="s">
         <v>127</v>
       </c>
@@ -2475,13 +2515,13 @@
         <v>40</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="D74">
-        <v>4.3863841746137902E-2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+        <v>389</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.0438638417461379</v>
+      </c>
+    </row>
+    <row r="75">
       <c r="A75" t="s">
         <v>90</v>
       </c>
@@ -2489,13 +2529,13 @@
         <v>40</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="D75">
-        <v>9.0534845632515501E-2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0905348456325155</v>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -2503,26 +2543,29 @@
         <v>40</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="D76">
-        <v>0.86078554000146901</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+        <v>391</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.860785540001469</v>
+      </c>
+    </row>
+    <row r="77">
       <c r="C77" s="7" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+      <c r="D77"/>
+    </row>
+    <row r="78">
       <c r="C78" s="7"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D78"/>
+    </row>
+    <row r="79">
       <c r="C79" s="2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+        <v>393</v>
+      </c>
+      <c r="D79"/>
+    </row>
+    <row r="80">
       <c r="A80" t="s">
         <v>209</v>
       </c>
@@ -2530,13 +2573,13 @@
         <v>40</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="D80">
+        <v>394</v>
+      </c>
+      <c r="D80" t="n">
         <v>0.101816314964547</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" s="8" t="s">
         <v>130</v>
       </c>
@@ -2544,13 +2587,13 @@
         <v>41</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="D81">
+        <v>395</v>
+      </c>
+      <c r="D81" t="n">
         <v>0.482396432723741</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" s="8" t="s">
         <v>131</v>
       </c>
@@ -2558,36 +2601,44 @@
         <v>42</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>393</v>
-      </c>
-      <c r="D82">
-        <v>0.66846316843403197</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+        <v>396</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.668463168434032</v>
+      </c>
+    </row>
+    <row r="83">
       <c r="A83" s="8"/>
       <c r="C83" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="D83"/>
+    </row>
+    <row r="84">
       <c r="A84" s="8"/>
       <c r="C84" s="7" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+        <v>397</v>
+      </c>
+      <c r="D84"/>
+    </row>
+    <row r="85">
       <c r="A85" s="8"/>
       <c r="C85" s="7" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+        <v>398</v>
+      </c>
+      <c r="D85"/>
+    </row>
+    <row r="86">
+      <c r="C86"/>
+      <c r="D86"/>
+    </row>
+    <row r="87">
       <c r="C87" s="2" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="D87"/>
+    </row>
+    <row r="88" ht="31" customHeight="1">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -2595,18 +2646,19 @@
         <v>40</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="D88">
-        <v>6.3792454461009604E-2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.0637924544610096</v>
+      </c>
+    </row>
+    <row r="89">
       <c r="C89" s="7" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+      <c r="D89"/>
+    </row>
+    <row r="90" ht="31" customHeight="1">
       <c r="A90" t="s">
         <v>89</v>
       </c>
@@ -2614,23 +2666,29 @@
         <v>40</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="D90">
+        <v>402</v>
+      </c>
+      <c r="D90" t="n">
         <v>0.165245904068308</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91">
+      <c r="C91"/>
+      <c r="D91"/>
+    </row>
+    <row r="92">
       <c r="C92" s="2" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>403</v>
+      </c>
+      <c r="D92"/>
+    </row>
+    <row r="93" ht="35.25" customHeight="1">
       <c r="C93" s="7" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+        <v>404</v>
+      </c>
+      <c r="D93"/>
+    </row>
+    <row r="94">
       <c r="A94" t="s">
         <v>75</v>
       </c>
@@ -2638,13 +2696,13 @@
         <v>40</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="D94">
-        <v>8.9112186820229103E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+        <v>405</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.0891121868202291</v>
+      </c>
+    </row>
+    <row r="95">
       <c r="A95" t="s">
         <v>78</v>
       </c>
@@ -2652,13 +2710,13 @@
         <v>40</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="D95">
+        <v>406</v>
+      </c>
+      <c r="D95" t="n">
         <v>0.120329734411022</v>
       </c>
     </row>
-    <row r="96" spans="1:4" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="31" customHeight="1">
       <c r="A96" t="s">
         <v>76</v>
       </c>
@@ -2666,13 +2724,13 @@
         <v>40</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="D96">
+        <v>407</v>
+      </c>
+      <c r="D96" t="n">
         <v>0.225051310926947</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>79</v>
       </c>
@@ -2680,13 +2738,13 @@
         <v>40</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="D97">
+        <v>408</v>
+      </c>
+      <c r="D97" t="n">
         <v>0.141283376763297</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>80</v>
       </c>
@@ -2694,13 +2752,13 @@
         <v>40</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D98">
-        <v>0.15966470170795699</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+        <v>409</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.159664701707957</v>
+      </c>
+    </row>
+    <row r="99">
       <c r="A99" t="s">
         <v>81</v>
       </c>
@@ -2708,13 +2766,13 @@
         <v>40</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="D99">
+        <v>410</v>
+      </c>
+      <c r="D99" t="n">
         <v>0.112900081914135</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>77</v>
       </c>
@@ -2722,18 +2780,23 @@
         <v>40</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D100">
-        <v>0.13351394828633001</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+        <v>411</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.13351394828633</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="C101"/>
+      <c r="D101"/>
+    </row>
+    <row r="102">
       <c r="C102" s="2" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+      <c r="D102"/>
+    </row>
+    <row r="103">
       <c r="A103" t="s">
         <v>72</v>
       </c>
@@ -2741,13 +2804,13 @@
         <v>40</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="D103">
-        <v>0.12122441098593099</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.121224410985931</v>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" t="s">
         <v>73</v>
       </c>
@@ -2755,13 +2818,13 @@
         <v>40</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="D104">
-        <v>0.81133960092391599</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.811339600923916</v>
+      </c>
+    </row>
+    <row r="105">
       <c r="A105" t="s">
         <v>74</v>
       </c>
@@ -2769,13 +2832,13 @@
         <v>40</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="D105">
-        <v>6.7435988081675002E-2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.067435988081675</v>
+      </c>
+    </row>
+    <row r="106">
       <c r="A106" t="s">
         <v>72</v>
       </c>
@@ -2783,13 +2846,13 @@
         <v>50</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="D106">
-        <v>8.7547552177706198E-2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.0875475521777062</v>
+      </c>
+    </row>
+    <row r="107">
       <c r="A107" t="s">
         <v>72</v>
       </c>
@@ -2797,34 +2860,35 @@
         <v>51</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="D107">
+        <v>417</v>
+      </c>
+      <c r="D107" t="n">
         <v>0.234572905806846</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="C108" t="s">
-        <v>324</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="D108"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C107"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="58.625" customWidth="1"/>
-    <col min="2" max="2" width="81.75" customWidth="1"/>
-    <col min="3" max="3" width="58.625" customWidth="1"/>
+    <col min="1" max="1" width="58.58203125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="81.75" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="58.58203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="5" t="s">
         <v>25</v>
       </c>
@@ -2832,10 +2896,10 @@
         <v>26</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -2843,10 +2907,10 @@
         <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>92</v>
       </c>
@@ -2854,10 +2918,10 @@
         <v>147</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
@@ -2865,10 +2929,10 @@
         <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
@@ -2876,10 +2940,10 @@
         <v>149</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -2887,10 +2951,10 @@
         <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>99</v>
       </c>
@@ -2898,10 +2962,10 @@
         <v>150</v>
       </c>
       <c r="C7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -2909,10 +2973,10 @@
         <v>151</v>
       </c>
       <c r="C8" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>94</v>
       </c>
@@ -2920,10 +2984,10 @@
         <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>95</v>
       </c>
@@ -2931,10 +2995,10 @@
         <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>96</v>
       </c>
@@ -2942,10 +3006,10 @@
         <v>154</v>
       </c>
       <c r="C11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>97</v>
       </c>
@@ -2953,10 +3017,10 @@
         <v>155</v>
       </c>
       <c r="C12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -2964,10 +3028,10 @@
         <v>156</v>
       </c>
       <c r="C13" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="4" t="s">
         <v>104</v>
       </c>
@@ -2975,10 +3039,10 @@
         <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="3" t="s">
         <v>98</v>
       </c>
@@ -2986,10 +3050,10 @@
         <v>158</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="4" t="s">
         <v>102</v>
       </c>
@@ -2997,10 +3061,10 @@
         <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
@@ -3008,10 +3072,10 @@
         <v>160</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>103</v>
       </c>
@@ -3019,10 +3083,10 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="6" t="s">
         <v>2</v>
       </c>
@@ -3030,10 +3094,10 @@
         <v>148</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" s="6" t="s">
         <v>3</v>
       </c>
@@ -3041,10 +3105,10 @@
         <v>149</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="6" t="s">
         <v>6</v>
       </c>
@@ -3052,10 +3116,10 @@
         <v>161</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" s="6" t="s">
         <v>7</v>
       </c>
@@ -3063,10 +3127,10 @@
         <v>162</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" s="6" t="s">
         <v>105</v>
       </c>
@@ -3074,10 +3138,10 @@
         <v>163</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -3085,10 +3149,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" s="6" t="s">
         <v>106</v>
       </c>
@@ -3096,10 +3160,10 @@
         <v>164</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="27" ht="31" customHeight="1">
       <c r="A27" s="7" t="s">
         <v>107</v>
       </c>
@@ -3107,10 +3171,10 @@
         <v>165</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" s="7" t="s">
         <v>9</v>
       </c>
@@ -3118,10 +3182,10 @@
         <v>166</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" s="7" t="s">
         <v>10</v>
       </c>
@@ -3129,10 +3193,10 @@
         <v>167</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" s="2" t="s">
         <v>11</v>
       </c>
@@ -3140,10 +3204,10 @@
         <v>168</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" s="7" t="s">
         <v>108</v>
       </c>
@@ -3151,10 +3215,10 @@
         <v>169</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" s="7" t="s">
         <v>85</v>
       </c>
@@ -3162,10 +3226,10 @@
         <v>170</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" s="7" t="s">
         <v>86</v>
       </c>
@@ -3173,10 +3237,10 @@
         <v>171</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" ht="31" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>12</v>
       </c>
@@ -3184,10 +3248,10 @@
         <v>172</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" s="7" t="s">
         <v>13</v>
       </c>
@@ -3195,10 +3259,10 @@
         <v>173</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="37" ht="31" customHeight="1">
       <c r="A37" s="7" t="s">
         <v>109</v>
       </c>
@@ -3206,10 +3270,10 @@
         <v>174</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" s="7" t="s">
         <v>111</v>
       </c>
@@ -3217,10 +3281,10 @@
         <v>175</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" s="2" t="s">
         <v>14</v>
       </c>
@@ -3228,10 +3292,10 @@
         <v>29</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1">
       <c r="A41" s="7" t="s">
         <v>112</v>
       </c>
@@ -3239,10 +3303,10 @@
         <v>176</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" s="7" t="s">
         <v>113</v>
       </c>
@@ -3250,10 +3314,10 @@
         <v>177</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" s="7" t="s">
         <v>114</v>
       </c>
@@ -3261,10 +3325,10 @@
         <v>178</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" s="7" t="s">
         <v>115</v>
       </c>
@@ -3272,10 +3336,10 @@
         <v>179</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" s="7" t="s">
         <v>115</v>
       </c>
@@ -3283,10 +3347,10 @@
         <v>179</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" s="7" t="s">
         <v>116</v>
       </c>
@@ -3294,10 +3358,10 @@
         <v>180</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" s="7" t="s">
         <v>116</v>
       </c>
@@ -3305,10 +3369,10 @@
         <v>180</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" s="7" t="s">
         <v>117</v>
       </c>
@@ -3316,10 +3380,10 @@
         <v>181</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49" ht="31" customHeight="1">
       <c r="A49" s="7" t="s">
         <v>118</v>
       </c>
@@ -3327,10 +3391,10 @@
         <v>182</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" s="7" t="s">
         <v>119</v>
       </c>
@@ -3338,10 +3402,10 @@
         <v>183</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" s="7" t="s">
         <v>120</v>
       </c>
@@ -3349,10 +3413,10 @@
         <v>184</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" s="7" t="s">
         <v>121</v>
       </c>
@@ -3360,10 +3424,10 @@
         <v>121</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" s="7" t="s">
         <v>122</v>
       </c>
@@ -3371,10 +3435,10 @@
         <v>185</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" s="2" t="s">
         <v>15</v>
       </c>
@@ -3382,21 +3446,21 @@
         <v>30</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" s="7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" s="7" t="s">
         <v>19</v>
       </c>
@@ -3404,10 +3468,10 @@
         <v>34</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" s="7" t="s">
         <v>18</v>
       </c>
@@ -3415,21 +3479,21 @@
         <v>33</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" s="7" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" s="7" t="s">
         <v>17</v>
       </c>
@@ -3437,10 +3501,10 @@
         <v>32</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" s="7" t="s">
         <v>16</v>
       </c>
@@ -3448,32 +3512,32 @@
         <v>31</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="B62" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B63" s="7" t="s">
-        <v>293</v>
-      </c>
       <c r="C63" s="7" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="65">
       <c r="A65" s="2" t="s">
         <v>20</v>
       </c>
@@ -3481,21 +3545,21 @@
         <v>186</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="66" ht="31" customHeight="1">
       <c r="A66" s="7" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="67">
       <c r="A67" s="7" t="s">
         <v>123</v>
       </c>
@@ -3503,10 +3567,10 @@
         <v>187</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="68" ht="31" customHeight="1">
       <c r="A68" s="7" t="s">
         <v>124</v>
       </c>
@@ -3514,10 +3578,10 @@
         <v>188</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="69">
       <c r="A69" s="7" t="s">
         <v>125</v>
       </c>
@@ -3525,10 +3589,10 @@
         <v>189</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="70">
       <c r="A70" s="7" t="s">
         <v>126</v>
       </c>
@@ -3536,26 +3600,26 @@
         <v>190</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="71">
       <c r="A71" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="C71" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="B71" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72">
       <c r="A72" s="7"/>
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" s="2" t="s">
         <v>21</v>
       </c>
@@ -3563,21 +3627,21 @@
         <v>191</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="74" ht="31" customHeight="1">
       <c r="A74" s="7" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="75">
       <c r="A75" s="7" t="s">
         <v>128</v>
       </c>
@@ -3585,10 +3649,10 @@
         <v>192</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="76">
       <c r="A76" s="7" t="s">
         <v>129</v>
       </c>
@@ -3596,26 +3660,26 @@
         <v>193</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="77">
       <c r="A77" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="78">
       <c r="A78" s="7"/>
       <c r="B78" s="7"/>
       <c r="C78" s="7"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" s="2" t="s">
         <v>22</v>
       </c>
@@ -3623,76 +3687,76 @@
         <v>35</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="80">
       <c r="A80" s="7" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="81">
       <c r="A81" s="7" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="82">
       <c r="A82" s="7" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83">
       <c r="A83" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="84">
       <c r="A84" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="85">
       <c r="A85" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="87">
       <c r="A87" s="2" t="s">
         <v>23</v>
       </c>
@@ -3700,10 +3764,10 @@
         <v>36</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="88" ht="31" customHeight="1">
       <c r="A88" s="7" t="s">
         <v>132</v>
       </c>
@@ -3711,10 +3775,10 @@
         <v>194</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="89">
       <c r="A89" s="7" t="s">
         <v>133</v>
       </c>
@@ -3722,10 +3786,10 @@
         <v>82</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="90" ht="31" customHeight="1">
       <c r="A90" s="7" t="s">
         <v>134</v>
       </c>
@@ -3733,10 +3797,10 @@
         <v>195</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="92">
       <c r="A92" s="2" t="s">
         <v>135</v>
       </c>
@@ -3744,10 +3808,10 @@
         <v>196</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="93" ht="31" customHeight="1">
       <c r="A93" s="7" t="s">
         <v>136</v>
       </c>
@@ -3755,10 +3819,10 @@
         <v>197</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="94">
       <c r="A94" s="7" t="s">
         <v>137</v>
       </c>
@@ -3766,10 +3830,10 @@
         <v>198</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="95">
       <c r="A95" s="7" t="s">
         <v>140</v>
       </c>
@@ -3777,10 +3841,10 @@
         <v>201</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="96" ht="31" customHeight="1">
       <c r="A96" s="7" t="s">
         <v>138</v>
       </c>
@@ -3788,10 +3852,10 @@
         <v>199</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="97">
       <c r="A97" s="7" t="s">
         <v>141</v>
       </c>
@@ -3799,10 +3863,10 @@
         <v>202</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="98">
       <c r="A98" s="7" t="s">
         <v>142</v>
       </c>
@@ -3810,10 +3874,10 @@
         <v>203</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="99">
       <c r="A99" s="7" t="s">
         <v>143</v>
       </c>
@@ -3821,10 +3885,10 @@
         <v>204</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="100">
       <c r="A100" s="7" t="s">
         <v>139</v>
       </c>
@@ -3832,10 +3896,10 @@
         <v>200</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="102">
       <c r="A102" s="2" t="s">
         <v>24</v>
       </c>
@@ -3843,43 +3907,43 @@
         <v>37</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="103">
       <c r="A103" s="7" t="s">
-        <v>325</v>
+        <v>210</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>414</v>
+        <v>288</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="104">
       <c r="A104" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="B104" s="7" t="s">
+      <c r="B105" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C104" s="7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>286</v>
-      </c>
       <c r="C105" s="7" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="106">
       <c r="A106" s="7" t="s">
         <v>144</v>
       </c>
@@ -3887,10 +3951,10 @@
         <v>205</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="107">
       <c r="A107" s="7" t="s">
         <v>145</v>
       </c>
@@ -3898,11 +3962,11 @@
         <v>206</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>